--- a/test data/New Hardware Data .xlsx
+++ b/test data/New Hardware Data .xlsx
@@ -1,20 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11114"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Desktop/all_SD_Practice_Code/documind/DocuMind/DocuMind/test data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{449EC8E0-BC93-A544-B1E3-3FC9EB79805E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="18940" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Hardware Sales" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Stock Summary" sheetId="2" r:id="rId6"/>
+    <sheet name="Hardware Sales" sheetId="1" r:id="rId1"/>
+    <sheet name="Stock Summary" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Hardware Sales'!$A$1:$R$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hardware Sales'!$A$1:$R$121</definedName>
   </definedNames>
-  <calcPr/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="124">
   <si>
     <t>INVOICE ID</t>
   </si>
@@ -386,162 +407,48 @@
   </si>
   <si>
     <t>Claw Hammer 16oz</t>
-  </si>
-  <si>
-    <t>HRD-002</t>
-  </si>
-  <si>
-    <t>Wheelbarrow Heavy Duty</t>
-  </si>
-  <si>
-    <t>PLB-004</t>
-  </si>
-  <si>
-    <t>Brass Tap 1/2"</t>
-  </si>
-  <si>
-    <t>PNT-001</t>
-  </si>
-  <si>
-    <t>Crown Silk Vinyl Emulsion 20L</t>
-  </si>
-  <si>
-    <t>Paints &amp; Finishes</t>
-  </si>
-  <si>
-    <t>Bucket</t>
-  </si>
-  <si>
-    <t>PNT-002</t>
-  </si>
-  <si>
-    <t>Basco Emulsion Paint 4L</t>
-  </si>
-  <si>
-    <t>Tin</t>
-  </si>
-  <si>
-    <t>PNT-004</t>
-  </si>
-  <si>
-    <t>Paint Roller 9" with Tray</t>
-  </si>
-  <si>
-    <t>PNT-005</t>
-  </si>
-  <si>
-    <t>Sika Tile Adhesive 20kg</t>
-  </si>
-  <si>
-    <t>PNT-006</t>
-  </si>
-  <si>
-    <t>Ceramic Floor Tile 40x40cm</t>
-  </si>
-  <si>
-    <t>Sq m</t>
-  </si>
-  <si>
-    <t>ROF-002</t>
-  </si>
-  <si>
-    <t>Box Profile Iron Sheet G28 3m</t>
-  </si>
-  <si>
-    <t>ROF-003</t>
-  </si>
-  <si>
-    <t>Roofing Nails 3" (per kg)</t>
-  </si>
-  <si>
-    <t>SAF-001</t>
-  </si>
-  <si>
-    <t>Safety Gumboots</t>
-  </si>
-  <si>
-    <t>Safety Gear</t>
-  </si>
-  <si>
-    <t>SAF-002</t>
-  </si>
-  <si>
-    <t>Work Gloves</t>
-  </si>
-  <si>
-    <t>STL-001</t>
-  </si>
-  <si>
-    <t>Y12 Steel Bar 12m</t>
-  </si>
-  <si>
-    <t>Steel &amp; Reinforcement</t>
-  </si>
-  <si>
-    <t>STL-002</t>
-  </si>
-  <si>
-    <t>Y10 Steel Bar 12m</t>
-  </si>
-  <si>
-    <t>STL-003</t>
-  </si>
-  <si>
-    <t>Y8 Steel Bar 12m</t>
-  </si>
-  <si>
-    <t>STL-004</t>
-  </si>
-  <si>
-    <t>Binding Wire (per kg)</t>
-  </si>
-  <si>
-    <t>STL-005</t>
-  </si>
-  <si>
-    <t>BRC Mesh A142 Sheet</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Quattrocento Sans"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Quattrocento Sans"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Quattrocento Sans"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Quattrocento Sans"/>
     </font>
     <font>
       <i/>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Quattrocento Sans"/>
     </font>
@@ -551,7 +458,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -561,12 +468,19 @@
     </fill>
   </fills>
   <borders count="3">
-    <border/>
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -581,68 +495,62 @@
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="14">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="4" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -650,7 +558,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -840,35 +748,35 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:R1000"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="28.0"/>
-    <col customWidth="1" min="2" max="2" width="13.0"/>
-    <col customWidth="1" min="3" max="3" width="30.0"/>
-    <col customWidth="1" min="4" max="4" width="18.0"/>
-    <col customWidth="1" min="5" max="5" width="11.0"/>
-    <col customWidth="1" min="6" max="6" width="34.0"/>
-    <col customWidth="1" min="7" max="8" width="22.0"/>
-    <col customWidth="1" min="9" max="9" width="9.0"/>
-    <col customWidth="1" min="10" max="10" width="10.0"/>
-    <col customWidth="1" min="11" max="12" width="16.0"/>
-    <col customWidth="1" min="13" max="13" width="13.0"/>
-    <col customWidth="1" min="14" max="14" width="17.0"/>
-    <col customWidth="1" min="15" max="15" width="19.0"/>
-    <col customWidth="1" min="16" max="16" width="15.0"/>
-    <col customWidth="1" min="17" max="17" width="14.0"/>
-    <col customWidth="1" min="18" max="18" width="16.0"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="6" max="6" width="34" customWidth="1"/>
+    <col min="7" max="8" width="22" customWidth="1"/>
+    <col min="9" max="9" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10" customWidth="1"/>
+    <col min="11" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
+    <col min="14" max="14" width="17" customWidth="1"/>
+    <col min="15" max="15" width="19" customWidth="1"/>
+    <col min="16" max="16" width="15" customWidth="1"/>
+    <col min="17" max="17" width="14" customWidth="1"/>
+    <col min="18" max="18" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -924,12 +832,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B2" s="3">
-        <v>46263.0</v>
+        <v>46263</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>19</v>
@@ -953,42 +861,42 @@
         <v>25</v>
       </c>
       <c r="J2" s="5">
-        <v>33.0</v>
+        <v>33</v>
       </c>
       <c r="K2" s="6">
-        <v>250.0</v>
+        <v>250</v>
       </c>
       <c r="L2" s="6">
-        <f t="shared" ref="L2:L15" si="1">J2*K2</f>
+        <f t="shared" ref="L2:L15" si="0">J2*K2</f>
         <v>8250</v>
       </c>
       <c r="M2" s="7">
         <v>0.16</v>
       </c>
       <c r="N2" s="6">
-        <f t="shared" ref="N2:N15" si="2">ROUND(L2*M2,2)</f>
+        <f t="shared" ref="N2:N15" si="1">ROUND(L2*M2,2)</f>
         <v>1320</v>
       </c>
       <c r="O2" s="6">
-        <f t="shared" ref="O2:O15" si="3">L2+N2</f>
+        <f t="shared" ref="O2:O15" si="2">L2+N2</f>
         <v>9570</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Q2" s="3">
-        <v>46266.0</v>
+        <v>46266</v>
       </c>
       <c r="R2" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B3" s="3">
-        <v>46263.0</v>
+        <v>46263</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>29</v>
@@ -1012,42 +920,42 @@
         <v>35</v>
       </c>
       <c r="J3" s="5">
-        <v>103.0</v>
+        <v>103</v>
       </c>
       <c r="K3" s="6">
-        <v>780.0</v>
+        <v>780</v>
       </c>
       <c r="L3" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>80340</v>
       </c>
       <c r="M3" s="7">
         <v>0.16</v>
       </c>
       <c r="N3" s="6">
+        <f t="shared" si="1"/>
+        <v>12854.4</v>
+      </c>
+      <c r="O3" s="6">
         <f t="shared" si="2"/>
-        <v>12854.4</v>
-      </c>
-      <c r="O3" s="6">
-        <f t="shared" si="3"/>
         <v>93194.4</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Q3" s="3">
-        <v>46277.0</v>
+        <v>46277</v>
       </c>
       <c r="R3" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="3">
-        <v>46265.0</v>
+        <v>46265</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>38</v>
@@ -1071,42 +979,42 @@
         <v>25</v>
       </c>
       <c r="J4" s="5">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="K4" s="6">
-        <v>650.0</v>
+        <v>650</v>
       </c>
       <c r="L4" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3250</v>
       </c>
       <c r="M4" s="7">
         <v>0.16</v>
       </c>
       <c r="N4" s="6">
+        <f t="shared" si="1"/>
+        <v>520</v>
+      </c>
+      <c r="O4" s="6">
         <f t="shared" si="2"/>
-        <v>520</v>
-      </c>
-      <c r="O4" s="6">
-        <f t="shared" si="3"/>
         <v>3770</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Q4" s="3">
-        <v>46269.0</v>
+        <v>46269</v>
       </c>
       <c r="R4" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>44</v>
       </c>
       <c r="B5" s="3">
-        <v>46265.0</v>
+        <v>46265</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>45</v>
@@ -1130,42 +1038,42 @@
         <v>50</v>
       </c>
       <c r="J5" s="5">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="K5" s="6">
-        <v>280.0</v>
+        <v>280</v>
       </c>
       <c r="L5" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>6440</v>
       </c>
       <c r="M5" s="7">
         <v>0.16</v>
       </c>
       <c r="N5" s="6">
+        <f t="shared" si="1"/>
+        <v>1030.4000000000001</v>
+      </c>
+      <c r="O5" s="6">
         <f t="shared" si="2"/>
-        <v>1030.4</v>
-      </c>
-      <c r="O5" s="6">
-        <f t="shared" si="3"/>
         <v>7470.4</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Q5" s="3">
-        <v>46275.0</v>
+        <v>46275</v>
       </c>
       <c r="R5" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>52</v>
       </c>
       <c r="B6" s="3">
-        <v>46267.0</v>
+        <v>46267</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>53</v>
@@ -1189,42 +1097,42 @@
         <v>59</v>
       </c>
       <c r="J6" s="5">
-        <v>132.0</v>
+        <v>132</v>
       </c>
       <c r="K6" s="6">
-        <v>850.0</v>
+        <v>850</v>
       </c>
       <c r="L6" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>112200</v>
       </c>
       <c r="M6" s="7">
         <v>0.16</v>
       </c>
       <c r="N6" s="6">
+        <f t="shared" si="1"/>
+        <v>17952</v>
+      </c>
+      <c r="O6" s="6">
         <f t="shared" si="2"/>
-        <v>17952</v>
-      </c>
-      <c r="O6" s="6">
-        <f t="shared" si="3"/>
         <v>130152</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Q6" s="3">
-        <v>46278.0</v>
+        <v>46278</v>
       </c>
       <c r="R6" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>60</v>
       </c>
       <c r="B7" s="3">
-        <v>46268.0</v>
+        <v>46268</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>61</v>
@@ -1248,42 +1156,42 @@
         <v>25</v>
       </c>
       <c r="J7" s="5">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="K7" s="6">
-        <v>650.0</v>
+        <v>650</v>
       </c>
       <c r="L7" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>11700</v>
       </c>
       <c r="M7" s="7">
         <v>0.16</v>
       </c>
       <c r="N7" s="6">
+        <f t="shared" si="1"/>
+        <v>1872</v>
+      </c>
+      <c r="O7" s="6">
         <f t="shared" si="2"/>
-        <v>1872</v>
-      </c>
-      <c r="O7" s="6">
-        <f t="shared" si="3"/>
         <v>13572</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Q7" s="3">
-        <v>46278.0</v>
+        <v>46278</v>
       </c>
       <c r="R7" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>66</v>
       </c>
       <c r="B8" s="3">
-        <v>46269.0</v>
+        <v>46269</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>53</v>
@@ -1307,42 +1215,42 @@
         <v>35</v>
       </c>
       <c r="J8" s="5">
-        <v>115.0</v>
+        <v>115</v>
       </c>
       <c r="K8" s="6">
-        <v>780.0</v>
+        <v>780</v>
       </c>
       <c r="L8" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>89700</v>
       </c>
       <c r="M8" s="7">
         <v>0.16</v>
       </c>
       <c r="N8" s="6">
+        <f t="shared" si="1"/>
+        <v>14352</v>
+      </c>
+      <c r="O8" s="6">
         <f t="shared" si="2"/>
-        <v>14352</v>
-      </c>
-      <c r="O8" s="6">
-        <f t="shared" si="3"/>
         <v>104052</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Q8" s="3">
-        <v>46282.0</v>
+        <v>46282</v>
       </c>
       <c r="R8" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>67</v>
       </c>
       <c r="B9" s="3">
-        <v>46269.0</v>
+        <v>46269</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>68</v>
@@ -1366,42 +1274,42 @@
         <v>35</v>
       </c>
       <c r="J9" s="5">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="K9" s="6">
-        <v>780.0</v>
+        <v>780</v>
       </c>
       <c r="L9" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2340</v>
       </c>
       <c r="M9" s="7">
         <v>0.16</v>
       </c>
       <c r="N9" s="6">
+        <f t="shared" si="1"/>
+        <v>374.4</v>
+      </c>
+      <c r="O9" s="6">
         <f t="shared" si="2"/>
-        <v>374.4</v>
-      </c>
-      <c r="O9" s="6">
-        <f t="shared" si="3"/>
         <v>2714.4</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Q9" s="3">
-        <v>46269.0</v>
+        <v>46269</v>
       </c>
       <c r="R9" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B10" s="3">
-        <v>46269.0</v>
+        <v>46269</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>72</v>
@@ -1425,42 +1333,42 @@
         <v>78</v>
       </c>
       <c r="J10" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="K10" s="6">
-        <v>8500.0</v>
+        <v>8500</v>
       </c>
       <c r="L10" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>17000</v>
       </c>
       <c r="M10" s="7">
         <v>0.16</v>
       </c>
       <c r="N10" s="6">
+        <f t="shared" si="1"/>
+        <v>2720</v>
+      </c>
+      <c r="O10" s="6">
         <f t="shared" si="2"/>
-        <v>2720</v>
-      </c>
-      <c r="O10" s="6">
-        <f t="shared" si="3"/>
         <v>19720</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Q10" s="3">
-        <v>46272.0</v>
+        <v>46272</v>
       </c>
       <c r="R10" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>79</v>
       </c>
       <c r="B11" s="3">
-        <v>46270.0</v>
+        <v>46270</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>45</v>
@@ -1484,42 +1392,42 @@
         <v>25</v>
       </c>
       <c r="J11" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="K11" s="6">
-        <v>650.0</v>
+        <v>650</v>
       </c>
       <c r="L11" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2600</v>
       </c>
       <c r="M11" s="7">
         <v>0.16</v>
       </c>
       <c r="N11" s="6">
+        <f t="shared" si="1"/>
+        <v>416</v>
+      </c>
+      <c r="O11" s="6">
         <f t="shared" si="2"/>
-        <v>416</v>
-      </c>
-      <c r="O11" s="6">
-        <f t="shared" si="3"/>
         <v>3016</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Q11" s="3">
-        <v>46270.0</v>
+        <v>46270</v>
       </c>
       <c r="R11" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>80</v>
       </c>
       <c r="B12" s="3">
-        <v>46270.0</v>
+        <v>46270</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>81</v>
@@ -1543,42 +1451,42 @@
         <v>25</v>
       </c>
       <c r="J12" s="5">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="K12" s="6">
-        <v>950.0</v>
+        <v>950</v>
       </c>
       <c r="L12" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>19000</v>
       </c>
       <c r="M12" s="7">
         <v>0.16</v>
       </c>
       <c r="N12" s="6">
+        <f t="shared" si="1"/>
+        <v>3040</v>
+      </c>
+      <c r="O12" s="6">
         <f t="shared" si="2"/>
-        <v>3040</v>
-      </c>
-      <c r="O12" s="6">
-        <f t="shared" si="3"/>
         <v>22040</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Q12" s="3">
-        <v>46273.0</v>
+        <v>46273</v>
       </c>
       <c r="R12" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>86</v>
       </c>
       <c r="B13" s="3">
-        <v>46270.0</v>
+        <v>46270</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>81</v>
@@ -1602,42 +1510,42 @@
         <v>25</v>
       </c>
       <c r="J13" s="5">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="K13" s="6">
-        <v>2400.0</v>
+        <v>2400</v>
       </c>
       <c r="L13" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>38400</v>
       </c>
       <c r="M13" s="7">
         <v>0.16</v>
       </c>
       <c r="N13" s="6">
+        <f t="shared" si="1"/>
+        <v>6144</v>
+      </c>
+      <c r="O13" s="6">
         <f t="shared" si="2"/>
-        <v>6144</v>
-      </c>
-      <c r="O13" s="6">
-        <f t="shared" si="3"/>
         <v>44544</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Q13" s="3">
-        <v>46280.0</v>
+        <v>46280</v>
       </c>
       <c r="R13" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>89</v>
       </c>
       <c r="B14" s="3">
-        <v>46272.0</v>
+        <v>46272</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>45</v>
@@ -1661,42 +1569,42 @@
         <v>92</v>
       </c>
       <c r="J14" s="5">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="K14" s="6">
-        <v>1450.0</v>
+        <v>1450</v>
       </c>
       <c r="L14" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>11600</v>
       </c>
       <c r="M14" s="7">
         <v>0.16</v>
       </c>
       <c r="N14" s="6">
+        <f t="shared" si="1"/>
+        <v>1856</v>
+      </c>
+      <c r="O14" s="6">
         <f t="shared" si="2"/>
-        <v>1856</v>
-      </c>
-      <c r="O14" s="6">
-        <f t="shared" si="3"/>
         <v>13456</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Q14" s="3">
-        <v>46278.0</v>
+        <v>46278</v>
       </c>
       <c r="R14" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B15" s="3">
-        <v>46272.0</v>
+        <v>46272</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>94</v>
@@ -1720,37 +1628,37 @@
         <v>59</v>
       </c>
       <c r="J15" s="5">
-        <v>47.0</v>
+        <v>47</v>
       </c>
       <c r="K15" s="6">
-        <v>850.0</v>
+        <v>850</v>
       </c>
       <c r="L15" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>39950</v>
       </c>
       <c r="M15" s="7">
         <v>0.16</v>
       </c>
       <c r="N15" s="6">
+        <f t="shared" si="1"/>
+        <v>6392</v>
+      </c>
+      <c r="O15" s="6">
         <f t="shared" si="2"/>
-        <v>6392</v>
-      </c>
-      <c r="O15" s="6">
-        <f t="shared" si="3"/>
         <v>46342</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>26</v>
       </c>
       <c r="Q15" s="3">
-        <v>46278.0</v>
+        <v>46278</v>
       </c>
       <c r="R15" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
       <c r="B16" s="3"/>
       <c r="C16" s="4"/>
@@ -1770,7 +1678,7 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="2"/>
     </row>
-    <row r="17">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
       <c r="B17" s="3"/>
       <c r="C17" s="4"/>
@@ -1790,7 +1698,7 @@
       <c r="Q17" s="3"/>
       <c r="R17" s="2"/>
     </row>
-    <row r="18">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
       <c r="B18" s="3"/>
       <c r="C18" s="4"/>
@@ -1810,7 +1718,7 @@
       <c r="Q18" s="3"/>
       <c r="R18" s="2"/>
     </row>
-    <row r="19">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
       <c r="B19" s="3"/>
       <c r="C19" s="4"/>
@@ -1830,7 +1738,7 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="2"/>
     </row>
-    <row r="20">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
       <c r="B20" s="3"/>
       <c r="C20" s="4"/>
@@ -1850,7 +1758,7 @@
       <c r="Q20" s="3"/>
       <c r="R20" s="2"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
+    <row r="21" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
       <c r="B21" s="3"/>
       <c r="C21" s="4"/>
@@ -1870,7 +1778,7 @@
       <c r="Q21" s="3"/>
       <c r="R21" s="2"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
+    <row r="22" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
       <c r="B22" s="3"/>
       <c r="C22" s="4"/>
@@ -1890,7 +1798,7 @@
       <c r="Q22" s="3"/>
       <c r="R22" s="2"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
+    <row r="23" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
       <c r="B23" s="3"/>
       <c r="C23" s="4"/>
@@ -1910,7 +1818,7 @@
       <c r="Q23" s="3"/>
       <c r="R23" s="2"/>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
+    <row r="24" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
       <c r="B24" s="3"/>
       <c r="C24" s="4"/>
@@ -1930,7 +1838,7 @@
       <c r="Q24" s="3"/>
       <c r="R24" s="2"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
+    <row r="25" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
       <c r="B25" s="3"/>
       <c r="C25" s="4"/>
@@ -1950,7 +1858,7 @@
       <c r="Q25" s="3"/>
       <c r="R25" s="2"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
+    <row r="26" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
       <c r="B26" s="3"/>
       <c r="C26" s="4"/>
@@ -1970,7 +1878,7 @@
       <c r="Q26" s="3"/>
       <c r="R26" s="2"/>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
+    <row r="27" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2"/>
       <c r="B27" s="3"/>
       <c r="C27" s="4"/>
@@ -1990,7 +1898,7 @@
       <c r="Q27" s="3"/>
       <c r="R27" s="2"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
+    <row r="28" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2"/>
       <c r="B28" s="3"/>
       <c r="C28" s="4"/>
@@ -2010,7 +1918,7 @@
       <c r="Q28" s="3"/>
       <c r="R28" s="2"/>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
+    <row r="29" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2"/>
       <c r="B29" s="3"/>
       <c r="C29" s="4"/>
@@ -2030,7 +1938,7 @@
       <c r="Q29" s="3"/>
       <c r="R29" s="2"/>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
+    <row r="30" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2"/>
       <c r="B30" s="3"/>
       <c r="C30" s="4"/>
@@ -2050,7 +1958,7 @@
       <c r="Q30" s="3"/>
       <c r="R30" s="2"/>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
+    <row r="31" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2"/>
       <c r="B31" s="3"/>
       <c r="C31" s="4"/>
@@ -2070,7 +1978,7 @@
       <c r="Q31" s="3"/>
       <c r="R31" s="2"/>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
+    <row r="32" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2"/>
       <c r="B32" s="3"/>
       <c r="C32" s="4"/>
@@ -2090,7 +1998,7 @@
       <c r="Q32" s="3"/>
       <c r="R32" s="2"/>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
+    <row r="33" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2"/>
       <c r="B33" s="3"/>
       <c r="C33" s="4"/>
@@ -2110,7 +2018,7 @@
       <c r="Q33" s="3"/>
       <c r="R33" s="2"/>
     </row>
-    <row r="34" ht="15.75" customHeight="1">
+    <row r="34" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2"/>
       <c r="B34" s="3"/>
       <c r="C34" s="4"/>
@@ -2130,7 +2038,7 @@
       <c r="Q34" s="3"/>
       <c r="R34" s="2"/>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
+    <row r="35" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2"/>
       <c r="B35" s="3"/>
       <c r="C35" s="4"/>
@@ -2150,7 +2058,7 @@
       <c r="Q35" s="3"/>
       <c r="R35" s="2"/>
     </row>
-    <row r="36" ht="15.75" customHeight="1">
+    <row r="36" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2"/>
       <c r="B36" s="3"/>
       <c r="C36" s="4"/>
@@ -2170,7 +2078,7 @@
       <c r="Q36" s="3"/>
       <c r="R36" s="2"/>
     </row>
-    <row r="37" ht="15.75" customHeight="1">
+    <row r="37" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2"/>
       <c r="B37" s="3"/>
       <c r="C37" s="4"/>
@@ -2190,7 +2098,7 @@
       <c r="Q37" s="3"/>
       <c r="R37" s="2"/>
     </row>
-    <row r="38" ht="15.75" customHeight="1">
+    <row r="38" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2"/>
       <c r="B38" s="3"/>
       <c r="C38" s="4"/>
@@ -2210,7 +2118,7 @@
       <c r="Q38" s="3"/>
       <c r="R38" s="2"/>
     </row>
-    <row r="39" ht="15.75" customHeight="1">
+    <row r="39" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2"/>
       <c r="B39" s="3"/>
       <c r="C39" s="4"/>
@@ -2230,7 +2138,7 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="2"/>
     </row>
-    <row r="40" ht="15.75" customHeight="1">
+    <row r="40" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2"/>
       <c r="B40" s="3"/>
       <c r="C40" s="4"/>
@@ -2250,7 +2158,7 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="2"/>
     </row>
-    <row r="41" ht="15.75" customHeight="1">
+    <row r="41" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2"/>
       <c r="B41" s="3"/>
       <c r="C41" s="4"/>
@@ -2270,7 +2178,7 @@
       <c r="Q41" s="3"/>
       <c r="R41" s="2"/>
     </row>
-    <row r="42" ht="15.75" customHeight="1">
+    <row r="42" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2"/>
       <c r="B42" s="3"/>
       <c r="C42" s="4"/>
@@ -2290,7 +2198,7 @@
       <c r="Q42" s="3"/>
       <c r="R42" s="2"/>
     </row>
-    <row r="43" ht="15.75" customHeight="1">
+    <row r="43" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2"/>
       <c r="B43" s="3"/>
       <c r="C43" s="4"/>
@@ -2310,7 +2218,7 @@
       <c r="Q43" s="3"/>
       <c r="R43" s="2"/>
     </row>
-    <row r="44" ht="15.75" customHeight="1">
+    <row r="44" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2"/>
       <c r="B44" s="3"/>
       <c r="C44" s="4"/>
@@ -2330,7 +2238,7 @@
       <c r="Q44" s="3"/>
       <c r="R44" s="2"/>
     </row>
-    <row r="45" ht="15.75" customHeight="1">
+    <row r="45" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2"/>
       <c r="B45" s="3"/>
       <c r="C45" s="4"/>
@@ -2350,7 +2258,7 @@
       <c r="Q45" s="3"/>
       <c r="R45" s="2"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1">
+    <row r="46" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2"/>
       <c r="B46" s="3"/>
       <c r="C46" s="4"/>
@@ -2370,7 +2278,7 @@
       <c r="Q46" s="3"/>
       <c r="R46" s="2"/>
     </row>
-    <row r="47" ht="15.75" customHeight="1">
+    <row r="47" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2"/>
       <c r="B47" s="3"/>
       <c r="C47" s="4"/>
@@ -2390,7 +2298,7 @@
       <c r="Q47" s="3"/>
       <c r="R47" s="2"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1">
+    <row r="48" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2"/>
       <c r="B48" s="3"/>
       <c r="C48" s="4"/>
@@ -2410,7 +2318,7 @@
       <c r="Q48" s="3"/>
       <c r="R48" s="2"/>
     </row>
-    <row r="49" ht="15.75" customHeight="1">
+    <row r="49" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2"/>
       <c r="B49" s="3"/>
       <c r="C49" s="4"/>
@@ -2430,7 +2338,7 @@
       <c r="Q49" s="3"/>
       <c r="R49" s="2"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1">
+    <row r="50" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2"/>
       <c r="B50" s="3"/>
       <c r="C50" s="4"/>
@@ -2450,7 +2358,7 @@
       <c r="Q50" s="3"/>
       <c r="R50" s="2"/>
     </row>
-    <row r="51" ht="15.75" customHeight="1">
+    <row r="51" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2"/>
       <c r="B51" s="3"/>
       <c r="C51" s="4"/>
@@ -2470,7 +2378,7 @@
       <c r="Q51" s="3"/>
       <c r="R51" s="2"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1">
+    <row r="52" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2"/>
       <c r="B52" s="3"/>
       <c r="C52" s="4"/>
@@ -2490,7 +2398,7 @@
       <c r="Q52" s="3"/>
       <c r="R52" s="2"/>
     </row>
-    <row r="53" ht="15.75" customHeight="1">
+    <row r="53" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2"/>
       <c r="B53" s="3"/>
       <c r="C53" s="4"/>
@@ -2510,7 +2418,7 @@
       <c r="Q53" s="3"/>
       <c r="R53" s="2"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
+    <row r="54" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2"/>
       <c r="B54" s="3"/>
       <c r="C54" s="4"/>
@@ -2530,7 +2438,7 @@
       <c r="Q54" s="3"/>
       <c r="R54" s="2"/>
     </row>
-    <row r="55" ht="15.75" customHeight="1">
+    <row r="55" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2"/>
       <c r="B55" s="3"/>
       <c r="C55" s="4"/>
@@ -2550,7 +2458,7 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="2"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1">
+    <row r="56" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2"/>
       <c r="B56" s="3"/>
       <c r="C56" s="4"/>
@@ -2570,7 +2478,7 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="2"/>
     </row>
-    <row r="57" ht="15.75" customHeight="1">
+    <row r="57" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2"/>
       <c r="B57" s="3"/>
       <c r="C57" s="4"/>
@@ -2590,7 +2498,7 @@
       <c r="Q57" s="3"/>
       <c r="R57" s="2"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1">
+    <row r="58" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2"/>
       <c r="B58" s="3"/>
       <c r="C58" s="4"/>
@@ -2610,7 +2518,7 @@
       <c r="Q58" s="3"/>
       <c r="R58" s="2"/>
     </row>
-    <row r="59" ht="15.75" customHeight="1">
+    <row r="59" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2"/>
       <c r="B59" s="3"/>
       <c r="C59" s="4"/>
@@ -2630,7 +2538,7 @@
       <c r="Q59" s="3"/>
       <c r="R59" s="2"/>
     </row>
-    <row r="60" ht="15.75" customHeight="1">
+    <row r="60" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2"/>
       <c r="B60" s="3"/>
       <c r="C60" s="4"/>
@@ -2650,7 +2558,7 @@
       <c r="Q60" s="3"/>
       <c r="R60" s="2"/>
     </row>
-    <row r="61" ht="15.75" customHeight="1">
+    <row r="61" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2"/>
       <c r="B61" s="3"/>
       <c r="C61" s="4"/>
@@ -2670,7 +2578,7 @@
       <c r="Q61" s="3"/>
       <c r="R61" s="2"/>
     </row>
-    <row r="62" ht="15.75" customHeight="1">
+    <row r="62" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2"/>
       <c r="B62" s="3"/>
       <c r="C62" s="4"/>
@@ -2690,7 +2598,7 @@
       <c r="Q62" s="3"/>
       <c r="R62" s="2"/>
     </row>
-    <row r="63" ht="15.75" customHeight="1">
+    <row r="63" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2"/>
       <c r="B63" s="3"/>
       <c r="C63" s="4"/>
@@ -2710,7 +2618,7 @@
       <c r="Q63" s="3"/>
       <c r="R63" s="2"/>
     </row>
-    <row r="64" ht="15.75" customHeight="1">
+    <row r="64" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2"/>
       <c r="B64" s="3"/>
       <c r="C64" s="4"/>
@@ -2730,7 +2638,7 @@
       <c r="Q64" s="3"/>
       <c r="R64" s="2"/>
     </row>
-    <row r="65" ht="15.75" customHeight="1">
+    <row r="65" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2"/>
       <c r="B65" s="3"/>
       <c r="C65" s="4"/>
@@ -2750,7 +2658,7 @@
       <c r="Q65" s="3"/>
       <c r="R65" s="2"/>
     </row>
-    <row r="66" ht="15.75" customHeight="1">
+    <row r="66" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2"/>
       <c r="B66" s="3"/>
       <c r="C66" s="4"/>
@@ -2770,7 +2678,7 @@
       <c r="Q66" s="3"/>
       <c r="R66" s="2"/>
     </row>
-    <row r="67" ht="15.75" customHeight="1">
+    <row r="67" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="2"/>
       <c r="B67" s="3"/>
       <c r="C67" s="4"/>
@@ -2790,7 +2698,7 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="2"/>
     </row>
-    <row r="68" ht="15.75" customHeight="1">
+    <row r="68" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2"/>
       <c r="B68" s="3"/>
       <c r="C68" s="4"/>
@@ -2810,7 +2718,7 @@
       <c r="Q68" s="3"/>
       <c r="R68" s="2"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1">
+    <row r="69" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="2"/>
       <c r="B69" s="3"/>
       <c r="C69" s="4"/>
@@ -2830,7 +2738,7 @@
       <c r="Q69" s="3"/>
       <c r="R69" s="2"/>
     </row>
-    <row r="70" ht="15.75" customHeight="1">
+    <row r="70" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="2"/>
       <c r="B70" s="3"/>
       <c r="C70" s="4"/>
@@ -2850,7 +2758,7 @@
       <c r="Q70" s="3"/>
       <c r="R70" s="2"/>
     </row>
-    <row r="71" ht="15.75" customHeight="1">
+    <row r="71" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="2"/>
       <c r="B71" s="3"/>
       <c r="C71" s="4"/>
@@ -2870,7 +2778,7 @@
       <c r="Q71" s="3"/>
       <c r="R71" s="2"/>
     </row>
-    <row r="72" ht="15.75" customHeight="1">
+    <row r="72" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="2"/>
       <c r="B72" s="3"/>
       <c r="C72" s="4"/>
@@ -2890,7 +2798,7 @@
       <c r="Q72" s="3"/>
       <c r="R72" s="2"/>
     </row>
-    <row r="73" ht="15.75" customHeight="1">
+    <row r="73" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="2"/>
       <c r="B73" s="3"/>
       <c r="C73" s="4"/>
@@ -2910,7 +2818,7 @@
       <c r="Q73" s="3"/>
       <c r="R73" s="2"/>
     </row>
-    <row r="74" ht="15.75" customHeight="1">
+    <row r="74" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="2"/>
       <c r="B74" s="3"/>
       <c r="C74" s="4"/>
@@ -2930,7 +2838,7 @@
       <c r="Q74" s="3"/>
       <c r="R74" s="2"/>
     </row>
-    <row r="75" ht="15.75" customHeight="1">
+    <row r="75" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="2"/>
       <c r="B75" s="3"/>
       <c r="C75" s="4"/>
@@ -2950,7 +2858,7 @@
       <c r="Q75" s="3"/>
       <c r="R75" s="2"/>
     </row>
-    <row r="76" ht="15.75" customHeight="1">
+    <row r="76" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="2"/>
       <c r="B76" s="3"/>
       <c r="C76" s="4"/>
@@ -2970,7 +2878,7 @@
       <c r="Q76" s="3"/>
       <c r="R76" s="2"/>
     </row>
-    <row r="77" ht="15.75" customHeight="1">
+    <row r="77" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="2"/>
       <c r="B77" s="3"/>
       <c r="C77" s="4"/>
@@ -2990,7 +2898,7 @@
       <c r="Q77" s="3"/>
       <c r="R77" s="2"/>
     </row>
-    <row r="78" ht="15.75" customHeight="1">
+    <row r="78" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="2"/>
       <c r="B78" s="3"/>
       <c r="C78" s="4"/>
@@ -3010,7 +2918,7 @@
       <c r="Q78" s="3"/>
       <c r="R78" s="2"/>
     </row>
-    <row r="79" ht="15.75" customHeight="1">
+    <row r="79" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="2"/>
       <c r="B79" s="3"/>
       <c r="C79" s="4"/>
@@ -3030,7 +2938,7 @@
       <c r="Q79" s="3"/>
       <c r="R79" s="2"/>
     </row>
-    <row r="80" ht="15.75" customHeight="1">
+    <row r="80" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="2"/>
       <c r="B80" s="3"/>
       <c r="C80" s="4"/>
@@ -3050,7 +2958,7 @@
       <c r="Q80" s="3"/>
       <c r="R80" s="2"/>
     </row>
-    <row r="81" ht="15.75" customHeight="1">
+    <row r="81" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="2"/>
       <c r="B81" s="3"/>
       <c r="C81" s="4"/>
@@ -3070,7 +2978,7 @@
       <c r="Q81" s="3"/>
       <c r="R81" s="2"/>
     </row>
-    <row r="82" ht="15.75" customHeight="1">
+    <row r="82" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="2"/>
       <c r="B82" s="3"/>
       <c r="C82" s="4"/>
@@ -3090,7 +2998,7 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="2"/>
     </row>
-    <row r="83" ht="15.75" customHeight="1">
+    <row r="83" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="2"/>
       <c r="B83" s="3"/>
       <c r="C83" s="4"/>
@@ -3110,7 +3018,7 @@
       <c r="Q83" s="2"/>
       <c r="R83" s="2"/>
     </row>
-    <row r="84" ht="15.75" customHeight="1">
+    <row r="84" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="2"/>
       <c r="B84" s="3"/>
       <c r="C84" s="4"/>
@@ -3130,7 +3038,7 @@
       <c r="Q84" s="3"/>
       <c r="R84" s="2"/>
     </row>
-    <row r="85" ht="15.75" customHeight="1">
+    <row r="85" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="2"/>
       <c r="B85" s="3"/>
       <c r="C85" s="4"/>
@@ -3150,7 +3058,7 @@
       <c r="Q85" s="3"/>
       <c r="R85" s="2"/>
     </row>
-    <row r="86" ht="15.75" customHeight="1">
+    <row r="86" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="2"/>
       <c r="B86" s="3"/>
       <c r="C86" s="4"/>
@@ -3170,7 +3078,7 @@
       <c r="Q86" s="3"/>
       <c r="R86" s="2"/>
     </row>
-    <row r="87" ht="15.75" customHeight="1">
+    <row r="87" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="2"/>
       <c r="B87" s="3"/>
       <c r="C87" s="4"/>
@@ -3190,7 +3098,7 @@
       <c r="Q87" s="2"/>
       <c r="R87" s="2"/>
     </row>
-    <row r="88" ht="15.75" customHeight="1">
+    <row r="88" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="2"/>
       <c r="B88" s="3"/>
       <c r="C88" s="4"/>
@@ -3210,7 +3118,7 @@
       <c r="Q88" s="3"/>
       <c r="R88" s="2"/>
     </row>
-    <row r="89" ht="15.75" customHeight="1">
+    <row r="89" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="2"/>
       <c r="B89" s="3"/>
       <c r="C89" s="4"/>
@@ -3230,7 +3138,7 @@
       <c r="Q89" s="2"/>
       <c r="R89" s="2"/>
     </row>
-    <row r="90" ht="15.75" customHeight="1">
+    <row r="90" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="2"/>
       <c r="B90" s="3"/>
       <c r="C90" s="4"/>
@@ -3250,7 +3158,7 @@
       <c r="Q90" s="2"/>
       <c r="R90" s="2"/>
     </row>
-    <row r="91" ht="15.75" customHeight="1">
+    <row r="91" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="2"/>
       <c r="B91" s="3"/>
       <c r="C91" s="4"/>
@@ -3270,7 +3178,7 @@
       <c r="Q91" s="3"/>
       <c r="R91" s="2"/>
     </row>
-    <row r="92" ht="15.75" customHeight="1">
+    <row r="92" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="2"/>
       <c r="B92" s="3"/>
       <c r="C92" s="4"/>
@@ -3290,7 +3198,7 @@
       <c r="Q92" s="3"/>
       <c r="R92" s="2"/>
     </row>
-    <row r="93" ht="15.75" customHeight="1">
+    <row r="93" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="2"/>
       <c r="B93" s="3"/>
       <c r="C93" s="4"/>
@@ -3310,7 +3218,7 @@
       <c r="Q93" s="3"/>
       <c r="R93" s="2"/>
     </row>
-    <row r="94" ht="15.75" customHeight="1">
+    <row r="94" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="2"/>
       <c r="B94" s="3"/>
       <c r="C94" s="4"/>
@@ -3330,7 +3238,7 @@
       <c r="Q94" s="3"/>
       <c r="R94" s="2"/>
     </row>
-    <row r="95" ht="15.75" customHeight="1">
+    <row r="95" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="2"/>
       <c r="B95" s="3"/>
       <c r="C95" s="4"/>
@@ -3350,7 +3258,7 @@
       <c r="Q95" s="2"/>
       <c r="R95" s="2"/>
     </row>
-    <row r="96" ht="15.75" customHeight="1">
+    <row r="96" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="2"/>
       <c r="B96" s="3"/>
       <c r="C96" s="4"/>
@@ -3370,7 +3278,7 @@
       <c r="Q96" s="2"/>
       <c r="R96" s="2"/>
     </row>
-    <row r="97" ht="15.75" customHeight="1">
+    <row r="97" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="2"/>
       <c r="B97" s="3"/>
       <c r="C97" s="4"/>
@@ -3390,7 +3298,7 @@
       <c r="Q97" s="2"/>
       <c r="R97" s="2"/>
     </row>
-    <row r="98" ht="15.75" customHeight="1">
+    <row r="98" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="2"/>
       <c r="B98" s="3"/>
       <c r="C98" s="4"/>
@@ -3410,7 +3318,7 @@
       <c r="Q98" s="2"/>
       <c r="R98" s="2"/>
     </row>
-    <row r="99" ht="15.75" customHeight="1">
+    <row r="99" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="2"/>
       <c r="B99" s="3"/>
       <c r="C99" s="4"/>
@@ -3430,7 +3338,7 @@
       <c r="Q99" s="2"/>
       <c r="R99" s="2"/>
     </row>
-    <row r="100" ht="15.75" customHeight="1">
+    <row r="100" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="2"/>
       <c r="B100" s="3"/>
       <c r="C100" s="4"/>
@@ -3450,7 +3358,7 @@
       <c r="Q100" s="2"/>
       <c r="R100" s="2"/>
     </row>
-    <row r="101" ht="15.75" customHeight="1">
+    <row r="101" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="2"/>
       <c r="B101" s="3"/>
       <c r="C101" s="4"/>
@@ -3470,7 +3378,7 @@
       <c r="Q101" s="3"/>
       <c r="R101" s="2"/>
     </row>
-    <row r="102" ht="15.75" customHeight="1">
+    <row r="102" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="2"/>
       <c r="B102" s="3"/>
       <c r="C102" s="4"/>
@@ -3490,7 +3398,7 @@
       <c r="Q102" s="3"/>
       <c r="R102" s="2"/>
     </row>
-    <row r="103" ht="15.75" customHeight="1">
+    <row r="103" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="2"/>
       <c r="B103" s="3"/>
       <c r="C103" s="4"/>
@@ -3510,7 +3418,7 @@
       <c r="Q103" s="2"/>
       <c r="R103" s="2"/>
     </row>
-    <row r="104" ht="15.75" customHeight="1">
+    <row r="104" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="2"/>
       <c r="B104" s="3"/>
       <c r="C104" s="4"/>
@@ -3530,7 +3438,7 @@
       <c r="Q104" s="3"/>
       <c r="R104" s="2"/>
     </row>
-    <row r="105" ht="15.75" customHeight="1">
+    <row r="105" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="2"/>
       <c r="B105" s="3"/>
       <c r="C105" s="4"/>
@@ -3550,7 +3458,7 @@
       <c r="Q105" s="3"/>
       <c r="R105" s="2"/>
     </row>
-    <row r="106" ht="15.75" customHeight="1">
+    <row r="106" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="2"/>
       <c r="B106" s="3"/>
       <c r="C106" s="4"/>
@@ -3570,7 +3478,7 @@
       <c r="Q106" s="2"/>
       <c r="R106" s="2"/>
     </row>
-    <row r="107" ht="15.75" customHeight="1">
+    <row r="107" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="2"/>
       <c r="B107" s="3"/>
       <c r="C107" s="4"/>
@@ -3590,7 +3498,7 @@
       <c r="Q107" s="3"/>
       <c r="R107" s="2"/>
     </row>
-    <row r="108" ht="15.75" customHeight="1">
+    <row r="108" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="2"/>
       <c r="B108" s="3"/>
       <c r="C108" s="4"/>
@@ -3610,7 +3518,7 @@
       <c r="Q108" s="3"/>
       <c r="R108" s="2"/>
     </row>
-    <row r="109" ht="15.75" customHeight="1">
+    <row r="109" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="2"/>
       <c r="B109" s="3"/>
       <c r="C109" s="4"/>
@@ -3630,7 +3538,7 @@
       <c r="Q109" s="3"/>
       <c r="R109" s="2"/>
     </row>
-    <row r="110" ht="15.75" customHeight="1">
+    <row r="110" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="2"/>
       <c r="B110" s="3"/>
       <c r="C110" s="4"/>
@@ -3650,7 +3558,7 @@
       <c r="Q110" s="2"/>
       <c r="R110" s="2"/>
     </row>
-    <row r="111" ht="15.75" customHeight="1">
+    <row r="111" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="2"/>
       <c r="B111" s="3"/>
       <c r="C111" s="4"/>
@@ -3670,7 +3578,7 @@
       <c r="Q111" s="2"/>
       <c r="R111" s="2"/>
     </row>
-    <row r="112" ht="15.75" customHeight="1">
+    <row r="112" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="2"/>
       <c r="B112" s="3"/>
       <c r="C112" s="4"/>
@@ -3690,7 +3598,7 @@
       <c r="Q112" s="2"/>
       <c r="R112" s="2"/>
     </row>
-    <row r="113" ht="15.75" customHeight="1">
+    <row r="113" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="2"/>
       <c r="B113" s="3"/>
       <c r="C113" s="4"/>
@@ -3710,7 +3618,7 @@
       <c r="Q113" s="3"/>
       <c r="R113" s="2"/>
     </row>
-    <row r="114" ht="15.75" customHeight="1">
+    <row r="114" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="2"/>
       <c r="B114" s="3"/>
       <c r="C114" s="4"/>
@@ -3730,7 +3638,7 @@
       <c r="Q114" s="2"/>
       <c r="R114" s="2"/>
     </row>
-    <row r="115" ht="15.75" customHeight="1">
+    <row r="115" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="2"/>
       <c r="B115" s="3"/>
       <c r="C115" s="4"/>
@@ -3750,7 +3658,7 @@
       <c r="Q115" s="3"/>
       <c r="R115" s="2"/>
     </row>
-    <row r="116" ht="15.75" customHeight="1">
+    <row r="116" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="2"/>
       <c r="B116" s="3"/>
       <c r="C116" s="4"/>
@@ -3770,7 +3678,7 @@
       <c r="Q116" s="2"/>
       <c r="R116" s="2"/>
     </row>
-    <row r="117" ht="15.75" customHeight="1">
+    <row r="117" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="2"/>
       <c r="B117" s="3"/>
       <c r="C117" s="4"/>
@@ -3790,7 +3698,7 @@
       <c r="Q117" s="2"/>
       <c r="R117" s="2"/>
     </row>
-    <row r="118" ht="15.75" customHeight="1">
+    <row r="118" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="2"/>
       <c r="B118" s="3"/>
       <c r="C118" s="4"/>
@@ -3810,7 +3718,7 @@
       <c r="Q118" s="2"/>
       <c r="R118" s="2"/>
     </row>
-    <row r="119" ht="15.75" customHeight="1">
+    <row r="119" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="2"/>
       <c r="B119" s="3"/>
       <c r="C119" s="4"/>
@@ -3830,7 +3738,7 @@
       <c r="Q119" s="2"/>
       <c r="R119" s="2"/>
     </row>
-    <row r="120" ht="15.75" customHeight="1">
+    <row r="120" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="2"/>
       <c r="B120" s="3"/>
       <c r="C120" s="4"/>
@@ -3850,7 +3758,7 @@
       <c r="Q120" s="2"/>
       <c r="R120" s="2"/>
     </row>
-    <row r="121" ht="15.75" customHeight="1">
+    <row r="121" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="2"/>
       <c r="B121" s="3"/>
       <c r="C121" s="4"/>
@@ -3870,7 +3778,7 @@
       <c r="Q121" s="3"/>
       <c r="R121" s="2"/>
     </row>
-    <row r="122" ht="15.75" customHeight="1">
+    <row r="122" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="K122" s="8" t="s">
         <v>96</v>
       </c>
@@ -3879,919 +3787,915 @@
         <v>442770</v>
       </c>
       <c r="N122" s="9">
-        <f t="shared" ref="N122:O122" si="4">SUM(N2:N121)</f>
-        <v>70843.2</v>
+        <f t="shared" ref="N122:O122" si="3">SUM(N2:N121)</f>
+        <v>70843.200000000012</v>
       </c>
       <c r="O122" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>513613.2</v>
       </c>
     </row>
-    <row r="123" ht="15.75" customHeight="1"/>
-    <row r="124" ht="15.75" customHeight="1"/>
-    <row r="125" ht="15.75" customHeight="1"/>
-    <row r="126" ht="15.75" customHeight="1"/>
-    <row r="127" ht="15.75" customHeight="1"/>
-    <row r="128" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
-    <row r="809" ht="15.75" customHeight="1"/>
-    <row r="810" ht="15.75" customHeight="1"/>
-    <row r="811" ht="15.75" customHeight="1"/>
-    <row r="812" ht="15.75" customHeight="1"/>
-    <row r="813" ht="15.75" customHeight="1"/>
-    <row r="814" ht="15.75" customHeight="1"/>
-    <row r="815" ht="15.75" customHeight="1"/>
-    <row r="816" ht="15.75" customHeight="1"/>
-    <row r="817" ht="15.75" customHeight="1"/>
-    <row r="818" ht="15.75" customHeight="1"/>
-    <row r="819" ht="15.75" customHeight="1"/>
-    <row r="820" ht="15.75" customHeight="1"/>
-    <row r="821" ht="15.75" customHeight="1"/>
-    <row r="822" ht="15.75" customHeight="1"/>
-    <row r="823" ht="15.75" customHeight="1"/>
-    <row r="824" ht="15.75" customHeight="1"/>
-    <row r="825" ht="15.75" customHeight="1"/>
-    <row r="826" ht="15.75" customHeight="1"/>
-    <row r="827" ht="15.75" customHeight="1"/>
-    <row r="828" ht="15.75" customHeight="1"/>
-    <row r="829" ht="15.75" customHeight="1"/>
-    <row r="830" ht="15.75" customHeight="1"/>
-    <row r="831" ht="15.75" customHeight="1"/>
-    <row r="832" ht="15.75" customHeight="1"/>
-    <row r="833" ht="15.75" customHeight="1"/>
-    <row r="834" ht="15.75" customHeight="1"/>
-    <row r="835" ht="15.75" customHeight="1"/>
-    <row r="836" ht="15.75" customHeight="1"/>
-    <row r="837" ht="15.75" customHeight="1"/>
-    <row r="838" ht="15.75" customHeight="1"/>
-    <row r="839" ht="15.75" customHeight="1"/>
-    <row r="840" ht="15.75" customHeight="1"/>
-    <row r="841" ht="15.75" customHeight="1"/>
-    <row r="842" ht="15.75" customHeight="1"/>
-    <row r="843" ht="15.75" customHeight="1"/>
-    <row r="844" ht="15.75" customHeight="1"/>
-    <row r="845" ht="15.75" customHeight="1"/>
-    <row r="846" ht="15.75" customHeight="1"/>
-    <row r="847" ht="15.75" customHeight="1"/>
-    <row r="848" ht="15.75" customHeight="1"/>
-    <row r="849" ht="15.75" customHeight="1"/>
-    <row r="850" ht="15.75" customHeight="1"/>
-    <row r="851" ht="15.75" customHeight="1"/>
-    <row r="852" ht="15.75" customHeight="1"/>
-    <row r="853" ht="15.75" customHeight="1"/>
-    <row r="854" ht="15.75" customHeight="1"/>
-    <row r="855" ht="15.75" customHeight="1"/>
-    <row r="856" ht="15.75" customHeight="1"/>
-    <row r="857" ht="15.75" customHeight="1"/>
-    <row r="858" ht="15.75" customHeight="1"/>
-    <row r="859" ht="15.75" customHeight="1"/>
-    <row r="860" ht="15.75" customHeight="1"/>
-    <row r="861" ht="15.75" customHeight="1"/>
-    <row r="862" ht="15.75" customHeight="1"/>
-    <row r="863" ht="15.75" customHeight="1"/>
-    <row r="864" ht="15.75" customHeight="1"/>
-    <row r="865" ht="15.75" customHeight="1"/>
-    <row r="866" ht="15.75" customHeight="1"/>
-    <row r="867" ht="15.75" customHeight="1"/>
-    <row r="868" ht="15.75" customHeight="1"/>
-    <row r="869" ht="15.75" customHeight="1"/>
-    <row r="870" ht="15.75" customHeight="1"/>
-    <row r="871" ht="15.75" customHeight="1"/>
-    <row r="872" ht="15.75" customHeight="1"/>
-    <row r="873" ht="15.75" customHeight="1"/>
-    <row r="874" ht="15.75" customHeight="1"/>
-    <row r="875" ht="15.75" customHeight="1"/>
-    <row r="876" ht="15.75" customHeight="1"/>
-    <row r="877" ht="15.75" customHeight="1"/>
-    <row r="878" ht="15.75" customHeight="1"/>
-    <row r="879" ht="15.75" customHeight="1"/>
-    <row r="880" ht="15.75" customHeight="1"/>
-    <row r="881" ht="15.75" customHeight="1"/>
-    <row r="882" ht="15.75" customHeight="1"/>
-    <row r="883" ht="15.75" customHeight="1"/>
-    <row r="884" ht="15.75" customHeight="1"/>
-    <row r="885" ht="15.75" customHeight="1"/>
-    <row r="886" ht="15.75" customHeight="1"/>
-    <row r="887" ht="15.75" customHeight="1"/>
-    <row r="888" ht="15.75" customHeight="1"/>
-    <row r="889" ht="15.75" customHeight="1"/>
-    <row r="890" ht="15.75" customHeight="1"/>
-    <row r="891" ht="15.75" customHeight="1"/>
-    <row r="892" ht="15.75" customHeight="1"/>
-    <row r="893" ht="15.75" customHeight="1"/>
-    <row r="894" ht="15.75" customHeight="1"/>
-    <row r="895" ht="15.75" customHeight="1"/>
-    <row r="896" ht="15.75" customHeight="1"/>
-    <row r="897" ht="15.75" customHeight="1"/>
-    <row r="898" ht="15.75" customHeight="1"/>
-    <row r="899" ht="15.75" customHeight="1"/>
-    <row r="900" ht="15.75" customHeight="1"/>
-    <row r="901" ht="15.75" customHeight="1"/>
-    <row r="902" ht="15.75" customHeight="1"/>
-    <row r="903" ht="15.75" customHeight="1"/>
-    <row r="904" ht="15.75" customHeight="1"/>
-    <row r="905" ht="15.75" customHeight="1"/>
-    <row r="906" ht="15.75" customHeight="1"/>
-    <row r="907" ht="15.75" customHeight="1"/>
-    <row r="908" ht="15.75" customHeight="1"/>
-    <row r="909" ht="15.75" customHeight="1"/>
-    <row r="910" ht="15.75" customHeight="1"/>
-    <row r="911" ht="15.75" customHeight="1"/>
-    <row r="912" ht="15.75" customHeight="1"/>
-    <row r="913" ht="15.75" customHeight="1"/>
-    <row r="914" ht="15.75" customHeight="1"/>
-    <row r="915" ht="15.75" customHeight="1"/>
-    <row r="916" ht="15.75" customHeight="1"/>
-    <row r="917" ht="15.75" customHeight="1"/>
-    <row r="918" ht="15.75" customHeight="1"/>
-    <row r="919" ht="15.75" customHeight="1"/>
-    <row r="920" ht="15.75" customHeight="1"/>
-    <row r="921" ht="15.75" customHeight="1"/>
-    <row r="922" ht="15.75" customHeight="1"/>
-    <row r="923" ht="15.75" customHeight="1"/>
-    <row r="924" ht="15.75" customHeight="1"/>
-    <row r="925" ht="15.75" customHeight="1"/>
-    <row r="926" ht="15.75" customHeight="1"/>
-    <row r="927" ht="15.75" customHeight="1"/>
-    <row r="928" ht="15.75" customHeight="1"/>
-    <row r="929" ht="15.75" customHeight="1"/>
-    <row r="930" ht="15.75" customHeight="1"/>
-    <row r="931" ht="15.75" customHeight="1"/>
-    <row r="932" ht="15.75" customHeight="1"/>
-    <row r="933" ht="15.75" customHeight="1"/>
-    <row r="934" ht="15.75" customHeight="1"/>
-    <row r="935" ht="15.75" customHeight="1"/>
-    <row r="936" ht="15.75" customHeight="1"/>
-    <row r="937" ht="15.75" customHeight="1"/>
-    <row r="938" ht="15.75" customHeight="1"/>
-    <row r="939" ht="15.75" customHeight="1"/>
-    <row r="940" ht="15.75" customHeight="1"/>
-    <row r="941" ht="15.75" customHeight="1"/>
-    <row r="942" ht="15.75" customHeight="1"/>
-    <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
-    <row r="945" ht="15.75" customHeight="1"/>
-    <row r="946" ht="15.75" customHeight="1"/>
-    <row r="947" ht="15.75" customHeight="1"/>
-    <row r="948" ht="15.75" customHeight="1"/>
-    <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1"/>
-    <row r="958" ht="15.75" customHeight="1"/>
-    <row r="959" ht="15.75" customHeight="1"/>
-    <row r="960" ht="15.75" customHeight="1"/>
-    <row r="961" ht="15.75" customHeight="1"/>
-    <row r="962" ht="15.75" customHeight="1"/>
-    <row r="963" ht="15.75" customHeight="1"/>
-    <row r="964" ht="15.75" customHeight="1"/>
-    <row r="965" ht="15.75" customHeight="1"/>
-    <row r="966" ht="15.75" customHeight="1"/>
-    <row r="967" ht="15.75" customHeight="1"/>
-    <row r="968" ht="15.75" customHeight="1"/>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1"/>
-    <row r="972" ht="15.75" customHeight="1"/>
-    <row r="973" ht="15.75" customHeight="1"/>
-    <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
-    <row r="976" ht="15.75" customHeight="1"/>
-    <row r="977" ht="15.75" customHeight="1"/>
-    <row r="978" ht="15.75" customHeight="1"/>
-    <row r="979" ht="15.75" customHeight="1"/>
-    <row r="980" ht="15.75" customHeight="1"/>
-    <row r="981" ht="15.75" customHeight="1"/>
-    <row r="982" ht="15.75" customHeight="1"/>
-    <row r="983" ht="15.75" customHeight="1"/>
-    <row r="984" ht="15.75" customHeight="1"/>
-    <row r="985" ht="15.75" customHeight="1"/>
-    <row r="986" ht="15.75" customHeight="1"/>
-    <row r="987" ht="15.75" customHeight="1"/>
-    <row r="988" ht="15.75" customHeight="1"/>
-    <row r="989" ht="15.75" customHeight="1"/>
-    <row r="990" ht="15.75" customHeight="1"/>
-    <row r="991" ht="15.75" customHeight="1"/>
-    <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="123" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <autoFilter ref="$A$1:$R$121"/>
-  <printOptions/>
-  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
+  <autoFilter ref="A1:R121" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:J976"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="11.0"/>
-    <col customWidth="1" min="2" max="2" width="34.0"/>
-    <col customWidth="1" min="3" max="3" width="22.0"/>
-    <col customWidth="1" min="4" max="4" width="9.0"/>
-    <col customWidth="1" min="5" max="5" width="14.0"/>
-    <col customWidth="1" min="6" max="6" width="12.0"/>
-    <col customWidth="1" min="7" max="9" width="14.0"/>
-    <col customWidth="1" min="10" max="10" width="22.0"/>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.5" customHeight="1">
+    <row r="1" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="10" t="s">
         <v>4</v>
       </c>
@@ -4823,7 +4727,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>103</v>
       </c>
@@ -4837,21 +4741,21 @@
         <v>25</v>
       </c>
       <c r="E2" s="11">
-        <v>3650.0</v>
+        <v>3650</v>
       </c>
       <c r="F2" s="5">
         <f>SUMIFS('Hardware Sales'!$J$2:$J$121,'Hardware Sales'!$E$2:$E$121,A2)</f>
         <v>0</v>
       </c>
       <c r="G2" s="5">
-        <f t="shared" ref="G2:G36" si="1">E2-F2</f>
+        <f t="shared" ref="G2:G12" si="0">E2-F2</f>
         <v>3650</v>
       </c>
       <c r="H2" s="11">
-        <v>730.0</v>
+        <v>730</v>
       </c>
       <c r="I2" s="2" t="str">
-        <f t="shared" ref="I2:I36" si="2">IF(G2&lt;=H2,"Reorder","OK")</f>
+        <f t="shared" ref="I2:I12" si="1">IF(G2&lt;=H2,"Reorder","OK")</f>
         <v>OK</v>
       </c>
       <c r="J2" s="6">
@@ -4859,7 +4763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>106</v>
       </c>
@@ -4873,21 +4777,21 @@
         <v>108</v>
       </c>
       <c r="E3" s="11">
-        <v>370.0</v>
+        <v>370</v>
       </c>
       <c r="F3" s="5">
         <f>SUMIFS('Hardware Sales'!$J$2:$J$121,'Hardware Sales'!$E$2:$E$121,A3)</f>
         <v>0</v>
       </c>
       <c r="G3" s="5">
+        <f t="shared" si="0"/>
+        <v>370</v>
+      </c>
+      <c r="H3" s="11">
+        <v>74</v>
+      </c>
+      <c r="I3" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>370</v>
-      </c>
-      <c r="H3" s="11">
-        <v>74.0</v>
-      </c>
-      <c r="I3" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>OK</v>
       </c>
       <c r="J3" s="6">
@@ -4895,7 +4799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>31</v>
       </c>
@@ -4909,21 +4813,21 @@
         <v>35</v>
       </c>
       <c r="E4" s="11">
-        <v>1120.0</v>
+        <v>1120</v>
       </c>
       <c r="F4" s="5">
         <f>SUMIFS('Hardware Sales'!$J$2:$J$121,'Hardware Sales'!$E$2:$E$121,A4)</f>
         <v>221</v>
       </c>
       <c r="G4" s="5">
+        <f t="shared" si="0"/>
+        <v>899</v>
+      </c>
+      <c r="H4" s="11">
+        <v>224</v>
+      </c>
+      <c r="I4" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>899</v>
-      </c>
-      <c r="H4" s="11">
-        <v>224.0</v>
-      </c>
-      <c r="I4" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>OK</v>
       </c>
       <c r="J4" s="6">
@@ -4931,7 +4835,7 @@
         <v>172380</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>109</v>
       </c>
@@ -4945,21 +4849,21 @@
         <v>35</v>
       </c>
       <c r="E5" s="11">
-        <v>280.0</v>
+        <v>280</v>
       </c>
       <c r="F5" s="5">
         <f>SUMIFS('Hardware Sales'!$J$2:$J$121,'Hardware Sales'!$E$2:$E$121,A5)</f>
         <v>0</v>
       </c>
       <c r="G5" s="5">
+        <f t="shared" si="0"/>
+        <v>280</v>
+      </c>
+      <c r="H5" s="11">
+        <v>56</v>
+      </c>
+      <c r="I5" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>280</v>
-      </c>
-      <c r="H5" s="11">
-        <v>56.0</v>
-      </c>
-      <c r="I5" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>OK</v>
       </c>
       <c r="J5" s="6">
@@ -4967,7 +4871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>111</v>
       </c>
@@ -4981,21 +4885,21 @@
         <v>35</v>
       </c>
       <c r="E6" s="11">
-        <v>430.0</v>
+        <v>430</v>
       </c>
       <c r="F6" s="5">
         <f>SUMIFS('Hardware Sales'!$J$2:$J$121,'Hardware Sales'!$E$2:$E$121,A6)</f>
         <v>0</v>
       </c>
       <c r="G6" s="5">
+        <f t="shared" si="0"/>
+        <v>430</v>
+      </c>
+      <c r="H6" s="11">
+        <v>86</v>
+      </c>
+      <c r="I6" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>430</v>
-      </c>
-      <c r="H6" s="11">
-        <v>86.0</v>
-      </c>
-      <c r="I6" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>OK</v>
       </c>
       <c r="J6" s="6">
@@ -5003,7 +4907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>113</v>
       </c>
@@ -5017,21 +4921,21 @@
         <v>115</v>
       </c>
       <c r="E7" s="11">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="F7" s="5">
         <f>SUMIFS('Hardware Sales'!$J$2:$J$121,'Hardware Sales'!$E$2:$E$121,A7)</f>
         <v>0</v>
       </c>
       <c r="G7" s="5">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="H7" s="11">
+        <v>5</v>
+      </c>
+      <c r="I7" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
-      <c r="H7" s="11">
-        <v>5.0</v>
-      </c>
-      <c r="I7" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>OK</v>
       </c>
       <c r="J7" s="6">
@@ -5039,7 +4943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>116</v>
       </c>
@@ -5053,21 +4957,21 @@
         <v>115</v>
       </c>
       <c r="E8" s="11">
-        <v>40.0</v>
+        <v>40</v>
       </c>
       <c r="F8" s="5">
         <f>SUMIFS('Hardware Sales'!$J$2:$J$121,'Hardware Sales'!$E$2:$E$121,A8)</f>
         <v>0</v>
       </c>
       <c r="G8" s="5">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="H8" s="11">
+        <v>8</v>
+      </c>
+      <c r="I8" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="H8" s="11">
-        <v>8.0</v>
-      </c>
-      <c r="I8" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>OK</v>
       </c>
       <c r="J8" s="6">
@@ -5075,7 +4979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>118</v>
       </c>
@@ -5089,21 +4993,21 @@
         <v>25</v>
       </c>
       <c r="E9" s="11">
-        <v>52.0</v>
+        <v>52</v>
       </c>
       <c r="F9" s="5">
         <f>SUMIFS('Hardware Sales'!$J$2:$J$121,'Hardware Sales'!$E$2:$E$121,A9)</f>
         <v>0</v>
       </c>
       <c r="G9" s="5">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="H9" s="11">
+        <v>10</v>
+      </c>
+      <c r="I9" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>52</v>
-      </c>
-      <c r="H9" s="11">
-        <v>10.0</v>
-      </c>
-      <c r="I9" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>OK</v>
       </c>
       <c r="J9" s="6">
@@ -5111,7 +5015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>21</v>
       </c>
@@ -5125,21 +5029,21 @@
         <v>25</v>
       </c>
       <c r="E10" s="11">
-        <v>120.0</v>
+        <v>120</v>
       </c>
       <c r="F10" s="5">
         <f>SUMIFS('Hardware Sales'!$J$2:$J$121,'Hardware Sales'!$E$2:$E$121,A10)</f>
         <v>33</v>
       </c>
       <c r="G10" s="5">
+        <f t="shared" si="0"/>
+        <v>87</v>
+      </c>
+      <c r="H10" s="11">
+        <v>24</v>
+      </c>
+      <c r="I10" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>87</v>
-      </c>
-      <c r="H10" s="11">
-        <v>24.0</v>
-      </c>
-      <c r="I10" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>OK</v>
       </c>
       <c r="J10" s="6">
@@ -5147,7 +5051,7 @@
         <v>8250</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>120</v>
       </c>
@@ -5161,21 +5065,21 @@
         <v>25</v>
       </c>
       <c r="E11" s="11">
-        <v>150.0</v>
+        <v>150</v>
       </c>
       <c r="F11" s="5">
         <f>SUMIFS('Hardware Sales'!$J$2:$J$121,'Hardware Sales'!$E$2:$E$121,A11)</f>
         <v>0</v>
       </c>
       <c r="G11" s="5">
+        <f t="shared" si="0"/>
+        <v>150</v>
+      </c>
+      <c r="H11" s="11">
+        <v>30</v>
+      </c>
+      <c r="I11" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>150</v>
-      </c>
-      <c r="H11" s="11">
-        <v>30.0</v>
-      </c>
-      <c r="I11" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>OK</v>
       </c>
       <c r="J11" s="6">
@@ -5183,7 +5087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>122</v>
       </c>
@@ -5197,21 +5101,21 @@
         <v>25</v>
       </c>
       <c r="E12" s="11">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="F12" s="5">
         <f>SUMIFS('Hardware Sales'!$J$2:$J$121,'Hardware Sales'!$E$2:$E$121,A12)</f>
         <v>0</v>
       </c>
       <c r="G12" s="5">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="H12" s="11">
+        <v>4</v>
+      </c>
+      <c r="I12" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-      <c r="H12" s="11">
-        <v>4.0</v>
-      </c>
-      <c r="I12" s="2" t="str">
-        <f t="shared" si="2"/>
         <v>OK</v>
       </c>
       <c r="J12" s="6">
@@ -5219,1856 +5123,990 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="11">
-        <v>15.0</v>
-      </c>
-      <c r="F13" s="5">
-        <f>SUMIFS('Hardware Sales'!$J$2:$J$121,'Hardware Sales'!$E$2:$E$121,A13)</f>
-        <v>0</v>
-      </c>
-      <c r="G13" s="5">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="H13" s="11">
-        <v>3.0</v>
-      </c>
-      <c r="I13" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>OK</v>
-      </c>
-      <c r="J13" s="6">
-        <f>SUMIFS('Hardware Sales'!$L$2:$L$121,'Hardware Sales'!$E$2:$E$121,A13)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" s="11">
-        <v>90.0</v>
-      </c>
-      <c r="F14" s="5">
-        <f>SUMIFS('Hardware Sales'!$J$2:$J$121,'Hardware Sales'!$E$2:$E$121,A14)</f>
-        <v>9</v>
-      </c>
-      <c r="G14" s="5">
-        <f t="shared" si="1"/>
-        <v>81</v>
-      </c>
-      <c r="H14" s="11">
-        <v>18.0</v>
-      </c>
-      <c r="I14" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>OK</v>
-      </c>
-      <c r="J14" s="6">
-        <f>SUMIFS('Hardware Sales'!$L$2:$L$121,'Hardware Sales'!$E$2:$E$121,A14)</f>
-        <v>5850</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E15" s="11">
-        <v>62.0</v>
-      </c>
-      <c r="F15" s="5">
-        <f>SUMIFS('Hardware Sales'!$J$2:$J$121,'Hardware Sales'!$E$2:$E$121,A15)</f>
-        <v>23</v>
-      </c>
-      <c r="G15" s="5">
-        <f t="shared" si="1"/>
-        <v>39</v>
-      </c>
-      <c r="H15" s="11">
-        <v>12.0</v>
-      </c>
-      <c r="I15" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>OK</v>
-      </c>
-      <c r="J15" s="6">
-        <f>SUMIFS('Hardware Sales'!$L$2:$L$121,'Hardware Sales'!$E$2:$E$121,A15)</f>
-        <v>6440</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E16" s="11">
-        <v>60.0</v>
-      </c>
-      <c r="F16" s="5">
-        <f>SUMIFS('Hardware Sales'!$J$2:$J$121,'Hardware Sales'!$E$2:$E$121,A16)</f>
-        <v>8</v>
-      </c>
-      <c r="G16" s="5">
-        <f t="shared" si="1"/>
-        <v>52</v>
-      </c>
-      <c r="H16" s="11">
-        <v>12.0</v>
-      </c>
-      <c r="I16" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>OK</v>
-      </c>
-      <c r="J16" s="6">
-        <f>SUMIFS('Hardware Sales'!$L$2:$L$121,'Hardware Sales'!$E$2:$E$121,A16)</f>
-        <v>11600</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" s="11">
-        <v>110.0</v>
-      </c>
-      <c r="F17" s="5">
-        <f>SUMIFS('Hardware Sales'!$J$2:$J$121,'Hardware Sales'!$E$2:$E$121,A17)</f>
-        <v>16</v>
-      </c>
-      <c r="G17" s="5">
-        <f t="shared" si="1"/>
-        <v>94</v>
-      </c>
-      <c r="H17" s="11">
-        <v>22.0</v>
-      </c>
-      <c r="I17" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>OK</v>
-      </c>
-      <c r="J17" s="6">
-        <f>SUMIFS('Hardware Sales'!$L$2:$L$121,'Hardware Sales'!$E$2:$E$121,A17)</f>
-        <v>38400</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="11">
-        <v>65.0</v>
-      </c>
-      <c r="F18" s="5">
-        <f>SUMIFS('Hardware Sales'!$J$2:$J$121,'Hardware Sales'!$E$2:$E$121,A18)</f>
-        <v>20</v>
-      </c>
-      <c r="G18" s="5">
-        <f t="shared" si="1"/>
-        <v>45</v>
-      </c>
-      <c r="H18" s="11">
-        <v>13.0</v>
-      </c>
-      <c r="I18" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>OK</v>
-      </c>
-      <c r="J18" s="6">
-        <f>SUMIFS('Hardware Sales'!$L$2:$L$121,'Hardware Sales'!$E$2:$E$121,A18)</f>
-        <v>19000</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E19" s="11">
-        <v>75.0</v>
-      </c>
-      <c r="F19" s="5">
-        <f>SUMIFS('Hardware Sales'!$J$2:$J$121,'Hardware Sales'!$E$2:$E$121,A19)</f>
-        <v>0</v>
-      </c>
-      <c r="G19" s="5">
-        <f t="shared" si="1"/>
-        <v>75</v>
-      </c>
-      <c r="H19" s="11">
-        <v>15.0</v>
-      </c>
-      <c r="I19" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>OK</v>
-      </c>
-      <c r="J19" s="6">
-        <f>SUMIFS('Hardware Sales'!$L$2:$L$121,'Hardware Sales'!$E$2:$E$121,A19)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E20" s="11">
-        <v>18.0</v>
-      </c>
-      <c r="F20" s="5">
-        <f>SUMIFS('Hardware Sales'!$J$2:$J$121,'Hardware Sales'!$E$2:$E$121,A20)</f>
-        <v>2</v>
-      </c>
-      <c r="G20" s="5">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="H20" s="11">
-        <v>4.0</v>
-      </c>
-      <c r="I20" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>OK</v>
-      </c>
-      <c r="J20" s="6">
-        <f>SUMIFS('Hardware Sales'!$L$2:$L$121,'Hardware Sales'!$E$2:$E$121,A20)</f>
-        <v>17000</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="E21" s="11">
-        <v>16.0</v>
-      </c>
-      <c r="F21" s="5">
-        <f>SUMIFS('Hardware Sales'!$J$2:$J$121,'Hardware Sales'!$E$2:$E$121,A21)</f>
-        <v>0</v>
-      </c>
-      <c r="G21" s="5">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="H21" s="11">
-        <v>3.0</v>
-      </c>
-      <c r="I21" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>OK</v>
-      </c>
-      <c r="J21" s="6">
-        <f>SUMIFS('Hardware Sales'!$L$2:$L$121,'Hardware Sales'!$E$2:$E$121,A21)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="E22" s="11">
-        <v>7.0</v>
-      </c>
-      <c r="F22" s="5">
-        <f>SUMIFS('Hardware Sales'!$J$2:$J$121,'Hardware Sales'!$E$2:$E$121,A22)</f>
-        <v>0</v>
-      </c>
-      <c r="G22" s="5">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="H22" s="11">
-        <v>2.0</v>
-      </c>
-      <c r="I22" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>OK</v>
-      </c>
-      <c r="J22" s="6">
-        <f>SUMIFS('Hardware Sales'!$L$2:$L$121,'Hardware Sales'!$E$2:$E$121,A22)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E23" s="11">
-        <v>60.0</v>
-      </c>
-      <c r="F23" s="5">
-        <f>SUMIFS('Hardware Sales'!$J$2:$J$121,'Hardware Sales'!$E$2:$E$121,A23)</f>
-        <v>0</v>
-      </c>
-      <c r="G23" s="5">
-        <f t="shared" si="1"/>
-        <v>60</v>
-      </c>
-      <c r="H23" s="11">
-        <v>12.0</v>
-      </c>
-      <c r="I23" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>OK</v>
-      </c>
-      <c r="J23" s="6">
-        <f>SUMIFS('Hardware Sales'!$L$2:$L$121,'Hardware Sales'!$E$2:$E$121,A23)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E24" s="11">
-        <v>70.0</v>
-      </c>
-      <c r="F24" s="5">
-        <f>SUMIFS('Hardware Sales'!$J$2:$J$121,'Hardware Sales'!$E$2:$E$121,A24)</f>
-        <v>0</v>
-      </c>
-      <c r="G24" s="5">
-        <f t="shared" si="1"/>
-        <v>70</v>
-      </c>
-      <c r="H24" s="11">
-        <v>14.0</v>
-      </c>
-      <c r="I24" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>OK</v>
-      </c>
-      <c r="J24" s="6">
-        <f>SUMIFS('Hardware Sales'!$L$2:$L$121,'Hardware Sales'!$E$2:$E$121,A24)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E25" s="11">
-        <v>280.0</v>
-      </c>
-      <c r="F25" s="5">
-        <f>SUMIFS('Hardware Sales'!$J$2:$J$121,'Hardware Sales'!$E$2:$E$121,A25)</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="5">
-        <f t="shared" si="1"/>
-        <v>280</v>
-      </c>
-      <c r="H25" s="11">
-        <v>56.0</v>
-      </c>
-      <c r="I25" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>OK</v>
-      </c>
-      <c r="J25" s="6">
-        <f>SUMIFS('Hardware Sales'!$L$2:$L$121,'Hardware Sales'!$E$2:$E$121,A25)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E26" s="11">
-        <v>840.0</v>
-      </c>
-      <c r="F26" s="5">
-        <f>SUMIFS('Hardware Sales'!$J$2:$J$121,'Hardware Sales'!$E$2:$E$121,A26)</f>
-        <v>179</v>
-      </c>
-      <c r="G26" s="5">
-        <f t="shared" si="1"/>
-        <v>661</v>
-      </c>
-      <c r="H26" s="11">
-        <v>168.0</v>
-      </c>
-      <c r="I26" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>OK</v>
-      </c>
-      <c r="J26" s="6">
-        <f>SUMIFS('Hardware Sales'!$L$2:$L$121,'Hardware Sales'!$E$2:$E$121,A26)</f>
-        <v>152150</v>
-      </c>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E27" s="11">
-        <v>320.0</v>
-      </c>
-      <c r="F27" s="5">
-        <f>SUMIFS('Hardware Sales'!$J$2:$J$121,'Hardware Sales'!$E$2:$E$121,A27)</f>
-        <v>0</v>
-      </c>
-      <c r="G27" s="5">
-        <f t="shared" si="1"/>
-        <v>320</v>
-      </c>
-      <c r="H27" s="11">
-        <v>64.0</v>
-      </c>
-      <c r="I27" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>OK</v>
-      </c>
-      <c r="J27" s="6">
-        <f>SUMIFS('Hardware Sales'!$L$2:$L$121,'Hardware Sales'!$E$2:$E$121,A27)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E28" s="11">
-        <v>180.0</v>
-      </c>
-      <c r="F28" s="5">
-        <f>SUMIFS('Hardware Sales'!$J$2:$J$121,'Hardware Sales'!$E$2:$E$121,A28)</f>
-        <v>0</v>
-      </c>
-      <c r="G28" s="5">
-        <f t="shared" si="1"/>
-        <v>180</v>
-      </c>
-      <c r="H28" s="11">
-        <v>36.0</v>
-      </c>
-      <c r="I28" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>OK</v>
-      </c>
-      <c r="J28" s="6">
-        <f>SUMIFS('Hardware Sales'!$L$2:$L$121,'Hardware Sales'!$E$2:$E$121,A28)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E29" s="11">
-        <v>140.0</v>
-      </c>
-      <c r="F29" s="5">
-        <f>SUMIFS('Hardware Sales'!$J$2:$J$121,'Hardware Sales'!$E$2:$E$121,A29)</f>
-        <v>18</v>
-      </c>
-      <c r="G29" s="5">
-        <f t="shared" si="1"/>
-        <v>122</v>
-      </c>
-      <c r="H29" s="11">
-        <v>28.0</v>
-      </c>
-      <c r="I29" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>OK</v>
-      </c>
-      <c r="J29" s="6">
-        <f>SUMIFS('Hardware Sales'!$L$2:$L$121,'Hardware Sales'!$E$2:$E$121,A29)</f>
-        <v>11700</v>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E30" s="11">
-        <v>55.0</v>
-      </c>
-      <c r="F30" s="5">
-        <f>SUMIFS('Hardware Sales'!$J$2:$J$121,'Hardware Sales'!$E$2:$E$121,A30)</f>
-        <v>0</v>
-      </c>
-      <c r="G30" s="5">
-        <f t="shared" si="1"/>
-        <v>55</v>
-      </c>
-      <c r="H30" s="11">
-        <v>11.0</v>
-      </c>
-      <c r="I30" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>OK</v>
-      </c>
-      <c r="J30" s="6">
-        <f>SUMIFS('Hardware Sales'!$L$2:$L$121,'Hardware Sales'!$E$2:$E$121,A30)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E31" s="11">
-        <v>170.0</v>
-      </c>
-      <c r="F31" s="5">
-        <f>SUMIFS('Hardware Sales'!$J$2:$J$121,'Hardware Sales'!$E$2:$E$121,A31)</f>
-        <v>0</v>
-      </c>
-      <c r="G31" s="5">
-        <f t="shared" si="1"/>
-        <v>170</v>
-      </c>
-      <c r="H31" s="11">
-        <v>34.0</v>
-      </c>
-      <c r="I31" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>OK</v>
-      </c>
-      <c r="J31" s="6">
-        <f>SUMIFS('Hardware Sales'!$L$2:$L$121,'Hardware Sales'!$E$2:$E$121,A31)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E32" s="11">
-        <v>180.0</v>
-      </c>
-      <c r="F32" s="5">
-        <f>SUMIFS('Hardware Sales'!$J$2:$J$121,'Hardware Sales'!$E$2:$E$121,A32)</f>
-        <v>0</v>
-      </c>
-      <c r="G32" s="5">
-        <f t="shared" si="1"/>
-        <v>180</v>
-      </c>
-      <c r="H32" s="11">
-        <v>36.0</v>
-      </c>
-      <c r="I32" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>OK</v>
-      </c>
-      <c r="J32" s="6">
-        <f>SUMIFS('Hardware Sales'!$L$2:$L$121,'Hardware Sales'!$E$2:$E$121,A32)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E33" s="11">
-        <v>66.0</v>
-      </c>
-      <c r="F33" s="5">
-        <f>SUMIFS('Hardware Sales'!$J$2:$J$121,'Hardware Sales'!$E$2:$E$121,A33)</f>
-        <v>0</v>
-      </c>
-      <c r="G33" s="5">
-        <f t="shared" si="1"/>
-        <v>66</v>
-      </c>
-      <c r="H33" s="11">
-        <v>13.0</v>
-      </c>
-      <c r="I33" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>OK</v>
-      </c>
-      <c r="J33" s="6">
-        <f>SUMIFS('Hardware Sales'!$L$2:$L$121,'Hardware Sales'!$E$2:$E$121,A33)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E34" s="11">
-        <v>65.0</v>
-      </c>
-      <c r="F34" s="5">
-        <f>SUMIFS('Hardware Sales'!$J$2:$J$121,'Hardware Sales'!$E$2:$E$121,A34)</f>
-        <v>0</v>
-      </c>
-      <c r="G34" s="5">
-        <f t="shared" si="1"/>
-        <v>65</v>
-      </c>
-      <c r="H34" s="11">
-        <v>13.0</v>
-      </c>
-      <c r="I34" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>OK</v>
-      </c>
-      <c r="J34" s="6">
-        <f>SUMIFS('Hardware Sales'!$L$2:$L$121,'Hardware Sales'!$E$2:$E$121,A34)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E35" s="11">
-        <v>12.0</v>
-      </c>
-      <c r="F35" s="5">
-        <f>SUMIFS('Hardware Sales'!$J$2:$J$121,'Hardware Sales'!$E$2:$E$121,A35)</f>
-        <v>0</v>
-      </c>
-      <c r="G35" s="5">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="H35" s="11">
-        <v>2.0</v>
-      </c>
-      <c r="I35" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>OK</v>
-      </c>
-      <c r="J35" s="6">
-        <f>SUMIFS('Hardware Sales'!$L$2:$L$121,'Hardware Sales'!$E$2:$E$121,A35)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E36" s="11">
-        <v>10.0</v>
-      </c>
-      <c r="F36" s="5">
-        <f>SUMIFS('Hardware Sales'!$J$2:$J$121,'Hardware Sales'!$E$2:$E$121,A36)</f>
-        <v>0</v>
-      </c>
-      <c r="G36" s="5">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="H36" s="11">
-        <v>2.0</v>
-      </c>
-      <c r="I36" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>OK</v>
-      </c>
-      <c r="J36" s="6">
-        <f>SUMIFS('Hardware Sales'!$L$2:$L$121,'Hardware Sales'!$E$2:$E$121,A36)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="I37" s="8" t="s">
+    <row r="13" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I13" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="J37" s="9">
-        <f>SUM(J2:J36)</f>
-        <v>442770</v>
-      </c>
-    </row>
-    <row r="38" ht="15.75" customHeight="1"/>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="12"/>
-    </row>
-    <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="13"/>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="13"/>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="13"/>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="13"/>
-    </row>
-    <row r="44" ht="15.75" customHeight="1"/>
-    <row r="45" ht="15.75" customHeight="1"/>
-    <row r="46" ht="15.75" customHeight="1"/>
-    <row r="47" ht="15.75" customHeight="1"/>
-    <row r="48" ht="15.75" customHeight="1"/>
-    <row r="49" ht="15.75" customHeight="1"/>
-    <row r="50" ht="15.75" customHeight="1"/>
-    <row r="51" ht="15.75" customHeight="1"/>
-    <row r="52" ht="15.75" customHeight="1"/>
-    <row r="53" ht="15.75" customHeight="1"/>
-    <row r="54" ht="15.75" customHeight="1"/>
-    <row r="55" ht="15.75" customHeight="1"/>
-    <row r="56" ht="15.75" customHeight="1"/>
-    <row r="57" ht="15.75" customHeight="1"/>
-    <row r="58" ht="15.75" customHeight="1"/>
-    <row r="59" ht="15.75" customHeight="1"/>
-    <row r="60" ht="15.75" customHeight="1"/>
-    <row r="61" ht="15.75" customHeight="1"/>
-    <row r="62" ht="15.75" customHeight="1"/>
-    <row r="63" ht="15.75" customHeight="1"/>
-    <row r="64" ht="15.75" customHeight="1"/>
-    <row r="65" ht="15.75" customHeight="1"/>
-    <row r="66" ht="15.75" customHeight="1"/>
-    <row r="67" ht="15.75" customHeight="1"/>
-    <row r="68" ht="15.75" customHeight="1"/>
-    <row r="69" ht="15.75" customHeight="1"/>
-    <row r="70" ht="15.75" customHeight="1"/>
-    <row r="71" ht="15.75" customHeight="1"/>
-    <row r="72" ht="15.75" customHeight="1"/>
-    <row r="73" ht="15.75" customHeight="1"/>
-    <row r="74" ht="15.75" customHeight="1"/>
-    <row r="75" ht="15.75" customHeight="1"/>
-    <row r="76" ht="15.75" customHeight="1"/>
-    <row r="77" ht="15.75" customHeight="1"/>
-    <row r="78" ht="15.75" customHeight="1"/>
-    <row r="79" ht="15.75" customHeight="1"/>
-    <row r="80" ht="15.75" customHeight="1"/>
-    <row r="81" ht="15.75" customHeight="1"/>
-    <row r="82" ht="15.75" customHeight="1"/>
-    <row r="83" ht="15.75" customHeight="1"/>
-    <row r="84" ht="15.75" customHeight="1"/>
-    <row r="85" ht="15.75" customHeight="1"/>
-    <row r="86" ht="15.75" customHeight="1"/>
-    <row r="87" ht="15.75" customHeight="1"/>
-    <row r="88" ht="15.75" customHeight="1"/>
-    <row r="89" ht="15.75" customHeight="1"/>
-    <row r="90" ht="15.75" customHeight="1"/>
-    <row r="91" ht="15.75" customHeight="1"/>
-    <row r="92" ht="15.75" customHeight="1"/>
-    <row r="93" ht="15.75" customHeight="1"/>
-    <row r="94" ht="15.75" customHeight="1"/>
-    <row r="95" ht="15.75" customHeight="1"/>
-    <row r="96" ht="15.75" customHeight="1"/>
-    <row r="97" ht="15.75" customHeight="1"/>
-    <row r="98" ht="15.75" customHeight="1"/>
-    <row r="99" ht="15.75" customHeight="1"/>
-    <row r="100" ht="15.75" customHeight="1"/>
-    <row r="101" ht="15.75" customHeight="1"/>
-    <row r="102" ht="15.75" customHeight="1"/>
-    <row r="103" ht="15.75" customHeight="1"/>
-    <row r="104" ht="15.75" customHeight="1"/>
-    <row r="105" ht="15.75" customHeight="1"/>
-    <row r="106" ht="15.75" customHeight="1"/>
-    <row r="107" ht="15.75" customHeight="1"/>
-    <row r="108" ht="15.75" customHeight="1"/>
-    <row r="109" ht="15.75" customHeight="1"/>
-    <row r="110" ht="15.75" customHeight="1"/>
-    <row r="111" ht="15.75" customHeight="1"/>
-    <row r="112" ht="15.75" customHeight="1"/>
-    <row r="113" ht="15.75" customHeight="1"/>
-    <row r="114" ht="15.75" customHeight="1"/>
-    <row r="115" ht="15.75" customHeight="1"/>
-    <row r="116" ht="15.75" customHeight="1"/>
-    <row r="117" ht="15.75" customHeight="1"/>
-    <row r="118" ht="15.75" customHeight="1"/>
-    <row r="119" ht="15.75" customHeight="1"/>
-    <row r="120" ht="15.75" customHeight="1"/>
-    <row r="121" ht="15.75" customHeight="1"/>
-    <row r="122" ht="15.75" customHeight="1"/>
-    <row r="123" ht="15.75" customHeight="1"/>
-    <row r="124" ht="15.75" customHeight="1"/>
-    <row r="125" ht="15.75" customHeight="1"/>
-    <row r="126" ht="15.75" customHeight="1"/>
-    <row r="127" ht="15.75" customHeight="1"/>
-    <row r="128" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
-    <row r="809" ht="15.75" customHeight="1"/>
-    <row r="810" ht="15.75" customHeight="1"/>
-    <row r="811" ht="15.75" customHeight="1"/>
-    <row r="812" ht="15.75" customHeight="1"/>
-    <row r="813" ht="15.75" customHeight="1"/>
-    <row r="814" ht="15.75" customHeight="1"/>
-    <row r="815" ht="15.75" customHeight="1"/>
-    <row r="816" ht="15.75" customHeight="1"/>
-    <row r="817" ht="15.75" customHeight="1"/>
-    <row r="818" ht="15.75" customHeight="1"/>
-    <row r="819" ht="15.75" customHeight="1"/>
-    <row r="820" ht="15.75" customHeight="1"/>
-    <row r="821" ht="15.75" customHeight="1"/>
-    <row r="822" ht="15.75" customHeight="1"/>
-    <row r="823" ht="15.75" customHeight="1"/>
-    <row r="824" ht="15.75" customHeight="1"/>
-    <row r="825" ht="15.75" customHeight="1"/>
-    <row r="826" ht="15.75" customHeight="1"/>
-    <row r="827" ht="15.75" customHeight="1"/>
-    <row r="828" ht="15.75" customHeight="1"/>
-    <row r="829" ht="15.75" customHeight="1"/>
-    <row r="830" ht="15.75" customHeight="1"/>
-    <row r="831" ht="15.75" customHeight="1"/>
-    <row r="832" ht="15.75" customHeight="1"/>
-    <row r="833" ht="15.75" customHeight="1"/>
-    <row r="834" ht="15.75" customHeight="1"/>
-    <row r="835" ht="15.75" customHeight="1"/>
-    <row r="836" ht="15.75" customHeight="1"/>
-    <row r="837" ht="15.75" customHeight="1"/>
-    <row r="838" ht="15.75" customHeight="1"/>
-    <row r="839" ht="15.75" customHeight="1"/>
-    <row r="840" ht="15.75" customHeight="1"/>
-    <row r="841" ht="15.75" customHeight="1"/>
-    <row r="842" ht="15.75" customHeight="1"/>
-    <row r="843" ht="15.75" customHeight="1"/>
-    <row r="844" ht="15.75" customHeight="1"/>
-    <row r="845" ht="15.75" customHeight="1"/>
-    <row r="846" ht="15.75" customHeight="1"/>
-    <row r="847" ht="15.75" customHeight="1"/>
-    <row r="848" ht="15.75" customHeight="1"/>
-    <row r="849" ht="15.75" customHeight="1"/>
-    <row r="850" ht="15.75" customHeight="1"/>
-    <row r="851" ht="15.75" customHeight="1"/>
-    <row r="852" ht="15.75" customHeight="1"/>
-    <row r="853" ht="15.75" customHeight="1"/>
-    <row r="854" ht="15.75" customHeight="1"/>
-    <row r="855" ht="15.75" customHeight="1"/>
-    <row r="856" ht="15.75" customHeight="1"/>
-    <row r="857" ht="15.75" customHeight="1"/>
-    <row r="858" ht="15.75" customHeight="1"/>
-    <row r="859" ht="15.75" customHeight="1"/>
-    <row r="860" ht="15.75" customHeight="1"/>
-    <row r="861" ht="15.75" customHeight="1"/>
-    <row r="862" ht="15.75" customHeight="1"/>
-    <row r="863" ht="15.75" customHeight="1"/>
-    <row r="864" ht="15.75" customHeight="1"/>
-    <row r="865" ht="15.75" customHeight="1"/>
-    <row r="866" ht="15.75" customHeight="1"/>
-    <row r="867" ht="15.75" customHeight="1"/>
-    <row r="868" ht="15.75" customHeight="1"/>
-    <row r="869" ht="15.75" customHeight="1"/>
-    <row r="870" ht="15.75" customHeight="1"/>
-    <row r="871" ht="15.75" customHeight="1"/>
-    <row r="872" ht="15.75" customHeight="1"/>
-    <row r="873" ht="15.75" customHeight="1"/>
-    <row r="874" ht="15.75" customHeight="1"/>
-    <row r="875" ht="15.75" customHeight="1"/>
-    <row r="876" ht="15.75" customHeight="1"/>
-    <row r="877" ht="15.75" customHeight="1"/>
-    <row r="878" ht="15.75" customHeight="1"/>
-    <row r="879" ht="15.75" customHeight="1"/>
-    <row r="880" ht="15.75" customHeight="1"/>
-    <row r="881" ht="15.75" customHeight="1"/>
-    <row r="882" ht="15.75" customHeight="1"/>
-    <row r="883" ht="15.75" customHeight="1"/>
-    <row r="884" ht="15.75" customHeight="1"/>
-    <row r="885" ht="15.75" customHeight="1"/>
-    <row r="886" ht="15.75" customHeight="1"/>
-    <row r="887" ht="15.75" customHeight="1"/>
-    <row r="888" ht="15.75" customHeight="1"/>
-    <row r="889" ht="15.75" customHeight="1"/>
-    <row r="890" ht="15.75" customHeight="1"/>
-    <row r="891" ht="15.75" customHeight="1"/>
-    <row r="892" ht="15.75" customHeight="1"/>
-    <row r="893" ht="15.75" customHeight="1"/>
-    <row r="894" ht="15.75" customHeight="1"/>
-    <row r="895" ht="15.75" customHeight="1"/>
-    <row r="896" ht="15.75" customHeight="1"/>
-    <row r="897" ht="15.75" customHeight="1"/>
-    <row r="898" ht="15.75" customHeight="1"/>
-    <row r="899" ht="15.75" customHeight="1"/>
-    <row r="900" ht="15.75" customHeight="1"/>
-    <row r="901" ht="15.75" customHeight="1"/>
-    <row r="902" ht="15.75" customHeight="1"/>
-    <row r="903" ht="15.75" customHeight="1"/>
-    <row r="904" ht="15.75" customHeight="1"/>
-    <row r="905" ht="15.75" customHeight="1"/>
-    <row r="906" ht="15.75" customHeight="1"/>
-    <row r="907" ht="15.75" customHeight="1"/>
-    <row r="908" ht="15.75" customHeight="1"/>
-    <row r="909" ht="15.75" customHeight="1"/>
-    <row r="910" ht="15.75" customHeight="1"/>
-    <row r="911" ht="15.75" customHeight="1"/>
-    <row r="912" ht="15.75" customHeight="1"/>
-    <row r="913" ht="15.75" customHeight="1"/>
-    <row r="914" ht="15.75" customHeight="1"/>
-    <row r="915" ht="15.75" customHeight="1"/>
-    <row r="916" ht="15.75" customHeight="1"/>
-    <row r="917" ht="15.75" customHeight="1"/>
-    <row r="918" ht="15.75" customHeight="1"/>
-    <row r="919" ht="15.75" customHeight="1"/>
-    <row r="920" ht="15.75" customHeight="1"/>
-    <row r="921" ht="15.75" customHeight="1"/>
-    <row r="922" ht="15.75" customHeight="1"/>
-    <row r="923" ht="15.75" customHeight="1"/>
-    <row r="924" ht="15.75" customHeight="1"/>
-    <row r="925" ht="15.75" customHeight="1"/>
-    <row r="926" ht="15.75" customHeight="1"/>
-    <row r="927" ht="15.75" customHeight="1"/>
-    <row r="928" ht="15.75" customHeight="1"/>
-    <row r="929" ht="15.75" customHeight="1"/>
-    <row r="930" ht="15.75" customHeight="1"/>
-    <row r="931" ht="15.75" customHeight="1"/>
-    <row r="932" ht="15.75" customHeight="1"/>
-    <row r="933" ht="15.75" customHeight="1"/>
-    <row r="934" ht="15.75" customHeight="1"/>
-    <row r="935" ht="15.75" customHeight="1"/>
-    <row r="936" ht="15.75" customHeight="1"/>
-    <row r="937" ht="15.75" customHeight="1"/>
-    <row r="938" ht="15.75" customHeight="1"/>
-    <row r="939" ht="15.75" customHeight="1"/>
-    <row r="940" ht="15.75" customHeight="1"/>
-    <row r="941" ht="15.75" customHeight="1"/>
-    <row r="942" ht="15.75" customHeight="1"/>
-    <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
-    <row r="945" ht="15.75" customHeight="1"/>
-    <row r="946" ht="15.75" customHeight="1"/>
-    <row r="947" ht="15.75" customHeight="1"/>
-    <row r="948" ht="15.75" customHeight="1"/>
-    <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1"/>
-    <row r="958" ht="15.75" customHeight="1"/>
-    <row r="959" ht="15.75" customHeight="1"/>
-    <row r="960" ht="15.75" customHeight="1"/>
-    <row r="961" ht="15.75" customHeight="1"/>
-    <row r="962" ht="15.75" customHeight="1"/>
-    <row r="963" ht="15.75" customHeight="1"/>
-    <row r="964" ht="15.75" customHeight="1"/>
-    <row r="965" ht="15.75" customHeight="1"/>
-    <row r="966" ht="15.75" customHeight="1"/>
-    <row r="967" ht="15.75" customHeight="1"/>
-    <row r="968" ht="15.75" customHeight="1"/>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1"/>
-    <row r="972" ht="15.75" customHeight="1"/>
-    <row r="973" ht="15.75" customHeight="1"/>
-    <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
-    <row r="976" ht="15.75" customHeight="1"/>
-    <row r="977" ht="15.75" customHeight="1"/>
-    <row r="978" ht="15.75" customHeight="1"/>
-    <row r="979" ht="15.75" customHeight="1"/>
-    <row r="980" ht="15.75" customHeight="1"/>
-    <row r="981" ht="15.75" customHeight="1"/>
-    <row r="982" ht="15.75" customHeight="1"/>
-    <row r="983" ht="15.75" customHeight="1"/>
-    <row r="984" ht="15.75" customHeight="1"/>
-    <row r="985" ht="15.75" customHeight="1"/>
-    <row r="986" ht="15.75" customHeight="1"/>
-    <row r="987" ht="15.75" customHeight="1"/>
-    <row r="988" ht="15.75" customHeight="1"/>
-    <row r="989" ht="15.75" customHeight="1"/>
-    <row r="990" ht="15.75" customHeight="1"/>
-    <row r="991" ht="15.75" customHeight="1"/>
-    <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
+      <c r="J13" s="9">
+        <f>SUM(J2:J12)</f>
+        <v>180630</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="15" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="12"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="13"/>
+    </row>
+    <row r="17" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="13"/>
+    </row>
+    <row r="18" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="13"/>
+    </row>
+    <row r="19" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="13"/>
+    </row>
+    <row r="20" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>